--- a/data/trans_orig/Hacinamiento_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2007</t>
+          <t>Hogares con dos o más personas por habitación en 2007 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35618</t>
+          <t>36499</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26805</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50927</t>
+          <t>50878</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46023</t>
+          <t>46147</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78181</t>
+          <t>81386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>655354</t>
+          <t>654473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>674801</t>
+          <t>675532</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>636429</t>
+          <t>636478</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>660551</t>
+          <t>661378</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1300147</t>
+          <t>1296942</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1332305</t>
+          <t>1332181</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43674</t>
+          <t>41402</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73105</t>
+          <t>71209</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48547</t>
+          <t>49095</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80060</t>
+          <t>83584</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98116</t>
+          <t>97928</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143144</t>
+          <t>142213</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>884838</t>
+          <t>886734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>914269</t>
+          <t>916541</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>886135</t>
+          <t>882611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>917648</t>
+          <t>917100</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1780993</t>
+          <t>1781924</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1826021</t>
+          <t>1826209</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15546</t>
+          <t>15506</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35680</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27275</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53182</t>
+          <t>51812</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48475</t>
+          <t>48364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81435</t>
+          <t>80865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>641843</t>
+          <t>640388</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661977</t>
+          <t>662017</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>629859</t>
+          <t>631229</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655766</t>
+          <t>655344</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1279130</t>
+          <t>1279700</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1312090</t>
+          <t>1312201</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39687</t>
+          <t>38679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68460</t>
+          <t>67463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48471</t>
+          <t>48688</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81182</t>
+          <t>80652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97121</t>
+          <t>96080</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139982</t>
+          <t>137996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>871225</t>
+          <t>872222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>899998</t>
+          <t>901006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>952508</t>
+          <t>953038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>985219</t>
+          <t>985002</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1833393</t>
+          <t>1835379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1876254</t>
+          <t>1877295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132020</t>
+          <t>133944</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>183004</t>
+          <t>187136</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>174184</t>
+          <t>173320</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>232663</t>
+          <t>231291</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>322844</t>
+          <t>323144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>400050</t>
+          <t>399602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3083118</t>
+          <t>3078986</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3134102</t>
+          <t>3132178</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3137619</t>
+          <t>3138991</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3196098</t>
+          <t>3196962</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6236354</t>
+          <t>6236802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6313560</t>
+          <t>6313260</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2012</t>
+          <t>Hogares con dos o más personas por habitación en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22293</t>
+          <t>22957</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44772</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20013</t>
+          <t>20120</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41642</t>
+          <t>42538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47809</t>
+          <t>47035</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78579</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>656933</t>
+          <t>656103</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>679412</t>
+          <t>678748</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>651125</t>
+          <t>650229</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>672754</t>
+          <t>672647</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1315892</t>
+          <t>1316079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1346662</t>
+          <t>1347436</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33620</t>
+          <t>34223</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60061</t>
+          <t>60714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47091</t>
+          <t>47948</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78045</t>
+          <t>79047</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89686</t>
+          <t>88554</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129926</t>
+          <t>129366</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>954724</t>
+          <t>954071</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>981165</t>
+          <t>980562</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>953089</t>
+          <t>952087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>984043</t>
+          <t>983186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1915993</t>
+          <t>1916553</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1956233</t>
+          <t>1957365</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31844</t>
+          <t>33529</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59995</t>
+          <t>62761</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56183</t>
+          <t>58302</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90344</t>
+          <t>90729</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95179</t>
+          <t>97277</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141122</t>
+          <t>141870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>692928</t>
+          <t>690162</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>721079</t>
+          <t>719394</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>682751</t>
+          <t>682366</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>716912</t>
+          <t>714793</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1384895</t>
+          <t>1384147</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1430838</t>
+          <t>1428740</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27766</t>
+          <t>27065</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51490</t>
+          <t>50840</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42866</t>
+          <t>43060</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73400</t>
+          <t>72689</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75994</t>
+          <t>77077</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113946</t>
+          <t>114357</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>893217</t>
+          <t>893867</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>916941</t>
+          <t>917642</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>973286</t>
+          <t>973997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1003820</t>
+          <t>1003626</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1877446</t>
+          <t>1877035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1915398</t>
+          <t>1914315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140369</t>
+          <t>137796</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>193221</t>
+          <t>188694</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>192329</t>
+          <t>190703</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>250007</t>
+          <t>249600</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>342485</t>
+          <t>348380</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>421320</t>
+          <t>421226</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3220899</t>
+          <t>3225426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3273751</t>
+          <t>3276324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3293674</t>
+          <t>3294081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3351352</t>
+          <t>3352978</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6536481</t>
+          <t>6536575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6615316</t>
+          <t>6609421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2016</t>
+          <t>Hogares con dos o más personas por habitación en 2016 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>21122</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45513</t>
+          <t>45902</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>18552</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>39768</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44542</t>
+          <t>44632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75214</t>
+          <t>75707</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>628241</t>
+          <t>627852</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>652380</t>
+          <t>652632</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>633224</t>
+          <t>632226</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>652948</t>
+          <t>653442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1270534</t>
+          <t>1270041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1301206</t>
+          <t>1301116</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25135</t>
+          <t>26262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50763</t>
+          <t>50406</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31578</t>
+          <t>30489</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56512</t>
+          <t>56144</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,47 +5020,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>78722</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>62445</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>99358</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,83%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>3,04%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>78722</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>59897</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>95643</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>967048</t>
+          <t>967405</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>992676</t>
+          <t>991549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>982155</t>
+          <t>982523</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1007089</t>
+          <t>1008178</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,47 +5133,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1848</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1977756</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1957120</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1994033</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>96,17%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>96,96%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1848</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1977756</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1960835</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1996581</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,17%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>95,35%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33740</t>
+          <t>32188</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62856</t>
+          <t>58718</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,49 +5328,49 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>50681</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>37989</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>65039</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>8,33%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>50681</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>37767</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>65306</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>8,36%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>87</t>
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78126</t>
+          <t>76647</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117360</t>
+          <t>116988</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>691752</t>
+          <t>695890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>720868</t>
+          <t>722420</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,47 +5441,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>92,22%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,73%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>730140</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>715782</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>742832</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>93,51%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>91,67%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>730140</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>715515</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>743054</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,51%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>91,64%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1418068</t>
+          <t>1418440</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1457302</t>
+          <t>1458781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21345</t>
+          <t>21774</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43685</t>
+          <t>42129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29321</t>
+          <t>29261</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55124</t>
+          <t>52958</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55852</t>
+          <t>54996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89715</t>
+          <t>88492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>885147</t>
+          <t>886703</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>907487</t>
+          <t>907058</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>979606</t>
+          <t>981772</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1005409</t>
+          <t>1005469</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1873847</t>
+          <t>1875070</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1907710</t>
+          <t>1908566</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>122364</t>
+          <t>121449</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171312</t>
+          <t>167990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136608</t>
+          <t>138065</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188378</t>
+          <t>189847</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>270698</t>
+          <t>270888</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>340004</t>
+          <t>339895</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3203692</t>
+          <t>3207014</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3252640</t>
+          <t>3253555</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3337833</t>
+          <t>3336364</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3389603</t>
+          <t>3388146</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6561212</t>
+          <t>6561321</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6630518</t>
+          <t>6630328</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2023</t>
+          <t>Hogares con dos o más personas por habitación en 2023 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33147</t>
+          <t>31247</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19059</t>
+          <t>19238</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>13197</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44844</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>596772</t>
+          <t>598672</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>625930</t>
+          <t>626214</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>701525</t>
+          <t>701346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>714383</t>
+          <t>713914</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1305659</t>
+          <t>1307351</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1336710</t>
+          <t>1337306</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9226</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33570</t>
+          <t>34379</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>13521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30879</t>
+          <t>30981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25662</t>
+          <t>25846</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56580</t>
+          <t>56382</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1150563</t>
+          <t>1149754</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1174907</t>
+          <t>1174369</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>916858</t>
+          <t>916756</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>933829</t>
+          <t>934216</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2075289</t>
+          <t>2075487</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2106207</t>
+          <t>2106023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33185</t>
+          <t>33165</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,82 +7275,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>27373</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12317</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>47650</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>47975</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>29227</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>71679</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>1,8%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>27373</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>12995</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>46168</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>47975</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>29604</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>68627</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668053</t>
+          <t>668073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>688588</t>
+          <t>688397</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7393,77 +7393,77 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>98,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>898507</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>878230</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>913563</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,04%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,85%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>98,67%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1643</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1579143</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1555439</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1597891</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>97,05%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>95,59%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>98,2%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>994</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>898507</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>879712</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>912885</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,04%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,01%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1643</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1579143</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1558491</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1597514</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>95,78%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>16396</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39930</t>
+          <t>38302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>22235</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43965</t>
+          <t>43468</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43839</t>
+          <t>45036</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>76978</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>877276</t>
+          <t>878904</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>899630</t>
+          <t>900810</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1039572</t>
+          <t>1040069</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1061821</t>
+          <t>1061302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1926501</t>
+          <t>1923766</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1956905</t>
+          <t>1955708</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56636</t>
+          <t>56103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105425</t>
+          <t>100191</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70590</t>
+          <t>69417</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114945</t>
+          <t>114009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>137769</t>
+          <t>136957</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>201908</t>
+          <t>201799</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3327070</t>
+          <t>3332304</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3375859</t>
+          <t>3376392</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3562794</t>
+          <t>3563730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3607149</t>
+          <t>3608322</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6908326</t>
+          <t>6908435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6972465</t>
+          <t>6973277</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Hacinamiento_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>15784</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36499</t>
+          <t>36851</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25978</t>
+          <t>26044</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50878</t>
+          <t>49962</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46147</t>
+          <t>46872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81386</t>
+          <t>77948</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>654473</t>
+          <t>654121</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>675532</t>
+          <t>675188</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>636478</t>
+          <t>637394</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>661378</t>
+          <t>661312</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1296942</t>
+          <t>1300380</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1332181</t>
+          <t>1331456</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41402</t>
+          <t>41774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71209</t>
+          <t>71379</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,82 +1091,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>63226</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>48677</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>81270</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>119256</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>99014</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>143042</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>6,2%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>7,43%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>63226</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>49095</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>83584</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>119256</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>97928</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>142213</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>886734</t>
+          <t>886564</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>916541</t>
+          <t>916169</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,82 +1204,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,64%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>902969</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>884925</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>917518</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>93,46%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>91,59%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>94,96%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1692</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1804881</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1781095</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1825123</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>93,8%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>92,57%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>902969</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>882611</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>917100</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,46%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>91,35%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>94,92%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1692</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1804881</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1781924</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1826209</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>93,8%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>92,61%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15506</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37135</t>
+          <t>36153</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27697</t>
+          <t>27088</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51812</t>
+          <t>52553</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48364</t>
+          <t>47521</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80865</t>
+          <t>80548</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640388</t>
+          <t>641370</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662017</t>
+          <t>661988</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>631229</t>
+          <t>630488</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655344</t>
+          <t>655953</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1279700</t>
+          <t>1280017</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1312201</t>
+          <t>1313044</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38679</t>
+          <t>40251</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67463</t>
+          <t>68820</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48688</t>
+          <t>49204</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80652</t>
+          <t>81205</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96080</t>
+          <t>95071</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137996</t>
+          <t>138191</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>872222</t>
+          <t>870865</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>901006</t>
+          <t>899434</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>953038</t>
+          <t>952485</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>985002</t>
+          <t>984486</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1835379</t>
+          <t>1835184</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1877295</t>
+          <t>1878304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>133944</t>
+          <t>133114</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187136</t>
+          <t>185742</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>173320</t>
+          <t>174603</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>231291</t>
+          <t>230064</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>323144</t>
+          <t>319328</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>399602</t>
+          <t>394110</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3078986</t>
+          <t>3080380</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3132178</t>
+          <t>3133008</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3138991</t>
+          <t>3140218</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3196962</t>
+          <t>3195679</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6236802</t>
+          <t>6242294</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6313260</t>
+          <t>6317076</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22957</t>
+          <t>22461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45602</t>
+          <t>44985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42538</t>
+          <t>41424</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47035</t>
+          <t>47759</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78392</t>
+          <t>78922</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>656103</t>
+          <t>656720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>678748</t>
+          <t>679244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>650229</t>
+          <t>651343</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>672647</t>
+          <t>673272</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1316079</t>
+          <t>1315549</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1347436</t>
+          <t>1346712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34223</t>
+          <t>35050</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60714</t>
+          <t>62288</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47948</t>
+          <t>47686</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79047</t>
+          <t>80419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88554</t>
+          <t>89393</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129366</t>
+          <t>131367</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>954071</t>
+          <t>952497</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>980562</t>
+          <t>979735</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>952087</t>
+          <t>950715</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>983186</t>
+          <t>983448</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1916553</t>
+          <t>1914552</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1957365</t>
+          <t>1956526</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33529</t>
+          <t>34896</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62761</t>
+          <t>61679</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58302</t>
+          <t>57144</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90729</t>
+          <t>91080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97277</t>
+          <t>98922</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141870</t>
+          <t>144628</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>690162</t>
+          <t>691244</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>719394</t>
+          <t>718027</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>682366</t>
+          <t>682015</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>714793</t>
+          <t>715951</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1384147</t>
+          <t>1381389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1428740</t>
+          <t>1427095</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27065</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50840</t>
+          <t>51400</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43060</t>
+          <t>43389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72689</t>
+          <t>71288</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77077</t>
+          <t>77495</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114357</t>
+          <t>115555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>893867</t>
+          <t>893307</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>917642</t>
+          <t>917163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>973997</t>
+          <t>975398</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1003626</t>
+          <t>1003297</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1877035</t>
+          <t>1875837</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1914315</t>
+          <t>1913897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>137796</t>
+          <t>139961</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>188694</t>
+          <t>188220</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>190703</t>
+          <t>193119</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>249600</t>
+          <t>250564</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>348380</t>
+          <t>344656</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>421226</t>
+          <t>421901</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3225426</t>
+          <t>3225900</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3276324</t>
+          <t>3274159</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3294081</t>
+          <t>3293117</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3352978</t>
+          <t>3350562</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6536575</t>
+          <t>6535900</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6609421</t>
+          <t>6613145</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21122</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45902</t>
+          <t>46282</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18552</t>
+          <t>18486</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39768</t>
+          <t>39411</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44632</t>
+          <t>45860</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75707</t>
+          <t>76513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>627852</t>
+          <t>627472</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>652632</t>
+          <t>652338</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>632226</t>
+          <t>632583</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>653442</t>
+          <t>653508</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1270041</t>
+          <t>1269235</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1301116</t>
+          <t>1299888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26262</t>
+          <t>26344</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50406</t>
+          <t>52351</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30489</t>
+          <t>31234</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56144</t>
+          <t>57414</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62445</t>
+          <t>60910</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99358</t>
+          <t>97254</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>967405</t>
+          <t>965460</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>991549</t>
+          <t>991467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>982523</t>
+          <t>981253</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1008178</t>
+          <t>1007433</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1957120</t>
+          <t>1959224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1994033</t>
+          <t>1995568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32188</t>
+          <t>32161</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58718</t>
+          <t>60336</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37989</t>
+          <t>38690</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65039</t>
+          <t>65682</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76647</t>
+          <t>77372</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116988</t>
+          <t>118278</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>695890</t>
+          <t>694272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>722420</t>
+          <t>722447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>715782</t>
+          <t>715139</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>742832</t>
+          <t>742131</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1418440</t>
+          <t>1417150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1458781</t>
+          <t>1458056</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21774</t>
+          <t>20858</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42129</t>
+          <t>43096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29261</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52958</t>
+          <t>53817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54996</t>
+          <t>56237</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88492</t>
+          <t>89876</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>886703</t>
+          <t>885736</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>907058</t>
+          <t>907974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>981772</t>
+          <t>980913</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1005469</t>
+          <t>1006153</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1875070</t>
+          <t>1873686</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1908566</t>
+          <t>1907325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>121449</t>
+          <t>121365</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>167990</t>
+          <t>171510</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>138065</t>
+          <t>135844</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189847</t>
+          <t>185701</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>270888</t>
+          <t>270054</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>339895</t>
+          <t>339993</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3207014</t>
+          <t>3203494</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3253555</t>
+          <t>3253639</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3336364</t>
+          <t>3340510</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3388146</t>
+          <t>3390367</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6561321</t>
+          <t>6561223</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6630328</t>
+          <t>6631162</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31247</t>
+          <t>27405</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19238</t>
+          <t>21388</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>21978</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>39921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>619399</t>
+          <t>673941</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>598672</t>
+          <t>657458</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>626214</t>
+          <t>680525</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>709126</t>
+          <t>715363</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>701346</t>
+          <t>707675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>713914</t>
+          <t>720912</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1328525</t>
+          <t>1389304</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1307351</t>
+          <t>1374005</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1337306</t>
+          <t>1399449</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>629919</t>
+          <t>684863</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>629919</t>
+          <t>684863</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>629919</t>
+          <t>684863</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>720584</t>
+          <t>729063</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>720584</t>
+          <t>729063</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>720584</t>
+          <t>729063</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1350503</t>
+          <t>1413926</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1350503</t>
+          <t>1413926</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1350503</t>
+          <t>1413926</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,67 +6912,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20286</t>
+          <t>27380</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>17556</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34379</t>
+          <t>40741</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>25355</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>18065</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>34991</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>20553</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>13521</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>30981</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>40838</t>
+          <t>52735</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25846</t>
+          <t>38725</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56382</t>
+          <t>67807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -7025,69 +7025,69 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1163847</t>
+          <t>1011853</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1149754</t>
+          <t>998492</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1174369</t>
+          <t>1021677</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>97,37%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1032819</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1023183</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1040109</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>98,29%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1466</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>927184</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>916756</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>934216</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,73%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2399</t>
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2091031</t>
+          <t>2044672</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2075487</t>
+          <t>2029600</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2106023</t>
+          <t>2058682</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1184133</t>
+          <t>1039233</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1184133</t>
+          <t>1039233</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1184133</t>
+          <t>1039233</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>947737</t>
+          <t>1058174</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>947737</t>
+          <t>1058174</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>947737</t>
+          <t>1058174</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2131869</t>
+          <t>2097407</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2131869</t>
+          <t>2097407</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2131869</t>
+          <t>2097407</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12841</t>
+          <t>19346</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33165</t>
+          <t>40371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27373</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>30373</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47650</t>
+          <t>60850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>47975</t>
+          <t>70711</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29227</t>
+          <t>54404</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71679</t>
+          <t>91256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>680637</t>
+          <t>770538</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668073</t>
+          <t>758465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>688397</t>
+          <t>779490</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>898507</t>
+          <t>761298</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>878230</t>
+          <t>742860</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>913563</t>
+          <t>773337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1579143</t>
+          <t>1531835</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1555439</t>
+          <t>1511290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1597891</t>
+          <t>1548142</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>701238</t>
+          <t>798836</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>701238</t>
+          <t>798836</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>701238</t>
+          <t>798836</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>925880</t>
+          <t>803710</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>925880</t>
+          <t>803710</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>925880</t>
+          <t>803710</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1627118</t>
+          <t>1602546</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1627118</t>
+          <t>1602546</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1627118</t>
+          <t>1602546</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26442</t>
+          <t>29764</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16396</t>
+          <t>20117</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38302</t>
+          <t>42738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31602</t>
+          <t>39144</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22235</t>
+          <t>28893</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43468</t>
+          <t>51091</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>58043</t>
+          <t>68908</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45036</t>
+          <t>54750</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76978</t>
+          <t>88390</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>890764</t>
+          <t>950874</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>878904</t>
+          <t>937900</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>900810</t>
+          <t>960521</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1051935</t>
+          <t>1069654</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1040069</t>
+          <t>1057707</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1061302</t>
+          <t>1079905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1942701</t>
+          <t>2020528</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1923766</t>
+          <t>2001046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1955708</t>
+          <t>2034686</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>917206</t>
+          <t>980638</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>917206</t>
+          <t>980638</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>917206</t>
+          <t>980638</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1083537</t>
+          <t>1108798</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1083537</t>
+          <t>1108798</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1083537</t>
+          <t>1108798</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2000744</t>
+          <t>2089436</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2000744</t>
+          <t>2089436</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2000744</t>
+          <t>2089436</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>77848</t>
+          <t>96365</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56103</t>
+          <t>76391</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100191</t>
+          <t>118263</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>90986</t>
+          <t>120611</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69417</t>
+          <t>101730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114009</t>
+          <t>144358</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>168834</t>
+          <t>216975</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>136957</t>
+          <t>189584</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>201799</t>
+          <t>248382</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3354647</t>
+          <t>3407205</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3332304</t>
+          <t>3385307</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3376392</t>
+          <t>3427179</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3586753</t>
+          <t>3579134</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3563730</t>
+          <t>3555387</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3608322</t>
+          <t>3598015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6941400</t>
+          <t>6986341</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6908435</t>
+          <t>6954934</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6973277</t>
+          <t>7013732</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3432495</t>
+          <t>3503570</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3432495</t>
+          <t>3503570</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3432495</t>
+          <t>3503570</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3677739</t>
+          <t>3699745</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3677739</t>
+          <t>3699745</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3677739</t>
+          <t>3699745</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7110234</t>
+          <t>7203316</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7110234</t>
+          <t>7203316</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7110234</t>
+          <t>7203316</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/Hacinamiento_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2007 (tasa de respuesta: 99,71%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2007 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2012 (tasa de respuesta: 99,62%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2016 (tasa de respuesta: 99,47%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2016 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2023 (tasa de respuesta: 99,08%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2023 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
